--- a/model/nop-auth-delta.orm.xlsx
+++ b/model/nop-auth-delta.orm.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\can\nop\nop-app-mall\model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FA60948-D06C-4A48-BDFC-B2A43392B036}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22B3EF22-050A-41BE-A294-AA2F728A0097}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" activeTab="1" xr2:uid="{BF79A538-0FD8-43E6-9CB3-F1057297980A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{BF79A538-0FD8-43E6-9CB3-F1057297980A}"/>
   </bookViews>
   <sheets>
     <sheet name="目录" sheetId="2" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="137">
   <si>
     <t>表名</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -553,24 +553,42 @@
   <si>
     <t>allowIdAsColName</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PIC_URL</t>
+  </si>
+  <si>
+    <t>Pic Url</t>
+  </si>
+  <si>
+    <t>测试图片</t>
+  </si>
+  <si>
+    <t>VARCHAR</t>
+  </si>
+  <si>
+    <t>file</t>
+  </si>
+  <si>
+    <t>image</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -578,7 +596,7 @@
     <font>
       <sz val="11"/>
       <color theme="8" tint="0.79998168889431442"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -587,7 +605,7 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -901,8 +919,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="超链接" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -918,9 +936,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -958,7 +976,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1064,7 +1082,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1206,7 +1224,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1215,14 +1233,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67E2504A-B138-424B-AD1A-08E9F1618FFC}">
   <dimension ref="A1:D24"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="5.6640625" customWidth="1"/>
-    <col min="2" max="3" width="19.58203125" customWidth="1"/>
-    <col min="4" max="4" width="16.5" customWidth="1"/>
+    <col min="2" max="3" width="19.5546875" customWidth="1"/>
+    <col min="4" max="4" width="16.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4">
       <c r="A1" s="2" t="s">
         <v>22</v>
       </c>
@@ -1236,7 +1254,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1248,7 +1266,7 @@
       </c>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1258,7 +1276,7 @@
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1268,7 +1286,7 @@
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1278,7 +1296,7 @@
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1288,7 +1306,7 @@
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1298,7 +1316,7 @@
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1308,7 +1326,7 @@
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1318,7 +1336,7 @@
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1328,7 +1346,7 @@
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1338,7 +1356,7 @@
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -1346,7 +1364,7 @@
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -1354,7 +1372,7 @@
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -1362,7 +1380,7 @@
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -1370,7 +1388,7 @@
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -1378,7 +1396,7 @@
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -1386,7 +1404,7 @@
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -1394,37 +1412,37 @@
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -1451,14 +1469,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9313AC94-4A2B-4F66-85AD-4A3D79664E62}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="22.08203125" customWidth="1"/>
-    <col min="2" max="2" width="27.9140625" customWidth="1"/>
-    <col min="3" max="3" width="39.25" customWidth="1"/>
+    <col min="1" max="1" width="22.109375" customWidth="1"/>
+    <col min="2" max="2" width="27.88671875" customWidth="1"/>
+    <col min="3" max="3" width="39.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="5" t="s">
         <v>100</v>
       </c>
@@ -1469,7 +1487,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
         <v>51</v>
       </c>
@@ -1480,7 +1498,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
         <v>62</v>
       </c>
@@ -1491,7 +1509,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
         <v>80</v>
       </c>
@@ -1502,7 +1520,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
         <v>78</v>
       </c>
@@ -1513,7 +1531,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
         <v>64</v>
       </c>
@@ -1524,7 +1542,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
         <v>65</v>
       </c>
@@ -1535,7 +1553,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
         <v>66</v>
       </c>
@@ -1546,7 +1564,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" s="1" t="s">
         <v>68</v>
       </c>
@@ -1557,7 +1575,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3">
       <c r="A10" s="1" t="s">
         <v>76</v>
       </c>
@@ -1568,7 +1586,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" ht="13.5" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>107</v>
       </c>
@@ -1577,7 +1595,7 @@
       </c>
       <c r="C11" s="1"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3">
       <c r="A12" s="1" t="s">
         <v>130</v>
       </c>
@@ -1586,22 +1604,22 @@
       </c>
       <c r="C12" s="1"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -1615,12 +1633,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF6B1C0B-16AE-459C-999C-D9C9CBAA7576}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="4.9140625" customWidth="1"/>
+    <col min="1" max="1" width="4.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" s="10" t="s">
         <v>22</v>
       </c>
@@ -1643,7 +1661,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2" s="7">
         <v>1</v>
       </c>
@@ -1660,14 +1678,16 @@
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="A3" s="7">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="1"/>
+      <c r="C3" s="1" t="s">
+        <v>135</v>
+      </c>
       <c r="D3" s="1" t="s">
         <v>29</v>
       </c>
@@ -1677,7 +1697,7 @@
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7">
       <c r="A4" s="7">
         <v>3</v>
       </c>
@@ -1694,7 +1714,7 @@
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7">
       <c r="A5" s="7">
         <v>4</v>
       </c>
@@ -1711,7 +1731,7 @@
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7">
       <c r="A6" s="7">
         <v>5</v>
       </c>
@@ -1728,7 +1748,7 @@
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7">
       <c r="A7" s="7">
         <v>6</v>
       </c>
@@ -1745,7 +1765,7 @@
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7">
       <c r="A8" s="7">
         <v>7</v>
       </c>
@@ -1762,7 +1782,7 @@
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7">
       <c r="A9" s="7">
         <v>8</v>
       </c>
@@ -1777,7 +1797,7 @@
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7">
       <c r="A10" s="7">
         <v>9</v>
       </c>
@@ -1794,7 +1814,7 @@
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7">
       <c r="A11" s="7">
         <v>10</v>
       </c>
@@ -1813,7 +1833,7 @@
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7">
       <c r="A12" s="7">
         <v>11</v>
       </c>
@@ -1830,7 +1850,7 @@
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7">
       <c r="A13" s="7">
         <v>12</v>
       </c>
@@ -1845,7 +1865,7 @@
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7">
       <c r="A14" s="7">
         <v>13</v>
       </c>
@@ -1860,7 +1880,7 @@
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7">
       <c r="A15" s="7">
         <v>14</v>
       </c>
@@ -1877,7 +1897,7 @@
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7">
       <c r="A16" s="7">
         <v>15</v>
       </c>
@@ -1892,7 +1912,7 @@
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7">
       <c r="A17" s="7">
         <v>16</v>
       </c>
@@ -1909,7 +1929,7 @@
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7">
       <c r="A18" s="7">
         <v>17</v>
       </c>
@@ -1926,7 +1946,7 @@
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -1935,7 +1955,7 @@
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -1944,7 +1964,7 @@
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -1953,7 +1973,7 @@
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -1962,7 +1982,7 @@
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -1971,7 +1991,7 @@
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -1980,7 +2000,7 @@
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -1989,7 +2009,7 @@
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -2006,25 +2026,25 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49753E9A-158A-4EB9-A449-F2590B12608A}">
-  <dimension ref="A1:P21"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:P22"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="4.33203125" customWidth="1"/>
-    <col min="2" max="2" width="4.5" customWidth="1"/>
-    <col min="3" max="3" width="8.1640625" customWidth="1"/>
+    <col min="2" max="2" width="4.44140625" customWidth="1"/>
+    <col min="3" max="3" width="8.109375" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="4.9140625" customWidth="1"/>
-    <col min="6" max="6" width="15.08203125" customWidth="1"/>
+    <col min="5" max="5" width="4.88671875" customWidth="1"/>
+    <col min="6" max="6" width="15.109375" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
-    <col min="9" max="9" width="4.75" customWidth="1"/>
+    <col min="9" max="9" width="4.77734375" customWidth="1"/>
     <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="6.08203125" customWidth="1"/>
-    <col min="12" max="12" width="7.4140625" customWidth="1"/>
+    <col min="11" max="11" width="6.109375" customWidth="1"/>
+    <col min="12" max="12" width="7.44140625" customWidth="1"/>
     <col min="13" max="13" width="9" customWidth="1"/>
-    <col min="14" max="14" width="6.5" customWidth="1"/>
+    <col min="14" max="14" width="6.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16">
       <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
@@ -2050,7 +2070,7 @@
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16">
       <c r="A2" s="18" t="s">
         <v>124</v>
       </c>
@@ -2076,7 +2096,7 @@
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16">
       <c r="A3" s="50" t="s">
         <v>4</v>
       </c>
@@ -2102,7 +2122,7 @@
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16">
       <c r="A4" s="50" t="s">
         <v>9</v>
       </c>
@@ -2122,7 +2142,7 @@
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16">
       <c r="A5" s="50" t="s">
         <v>10</v>
       </c>
@@ -2142,7 +2162,7 @@
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16">
       <c r="A6" s="30"/>
       <c r="B6" s="31"/>
       <c r="C6" s="31"/>
@@ -2160,7 +2180,7 @@
       <c r="O6" s="31"/>
       <c r="P6" s="32"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16">
       <c r="A7" s="47" t="s">
         <v>1</v>
       </c>
@@ -2180,7 +2200,7 @@
       <c r="O7" s="47"/>
       <c r="P7" s="47"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16">
       <c r="A8" s="2" t="s">
         <v>20</v>
       </c>
@@ -2230,7 +2250,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16">
       <c r="A9" s="7">
         <v>1</v>
       </c>
@@ -2270,7 +2290,7 @@
       <c r="O9" s="7"/>
       <c r="P9" s="1"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16">
       <c r="A10" s="7">
         <v>100</v>
       </c>
@@ -2298,30 +2318,28 @@
       <c r="O10" s="7"/>
       <c r="P10" s="1"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16">
       <c r="A11" s="7">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="B11" s="7"/>
-      <c r="C11" s="7" t="s">
-        <v>128</v>
-      </c>
+      <c r="C11" s="7"/>
       <c r="D11" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>96</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="E11" s="7"/>
       <c r="F11" s="9" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="H11" s="9"/>
+        <v>133</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>136</v>
+      </c>
       <c r="I11" s="7"/>
       <c r="J11" s="9" t="s">
-        <v>29</v>
+        <v>134</v>
       </c>
       <c r="K11" s="7">
         <v>100</v>
@@ -2332,212 +2350,228 @@
       <c r="O11" s="7"/>
       <c r="P11" s="1"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A13" s="42" t="s">
+    <row r="12" spans="1:16">
+      <c r="A12" s="7">
+        <v>26</v>
+      </c>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="H12" s="9"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="K12" s="7">
+        <v>100</v>
+      </c>
+      <c r="L12" s="7"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="9"/>
+      <c r="O12" s="7"/>
+      <c r="P12" s="1"/>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="43"/>
-      <c r="C13" s="43"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="43"/>
-      <c r="G13" s="43"/>
-      <c r="H13" s="43"/>
-      <c r="I13" s="43"/>
-      <c r="J13" s="43"/>
-      <c r="K13" s="43"/>
-      <c r="L13" s="43"/>
-      <c r="M13" s="43"/>
-      <c r="N13" s="43"/>
-      <c r="O13" s="43"/>
-      <c r="P13" s="44"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A14" s="45">
+      <c r="B14" s="43"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="43"/>
+      <c r="J14" s="43"/>
+      <c r="K14" s="43"/>
+      <c r="L14" s="43"/>
+      <c r="M14" s="43"/>
+      <c r="N14" s="43"/>
+      <c r="O14" s="43"/>
+      <c r="P14" s="44"/>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15" s="45">
         <v>1</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B15" s="18" t="s">
         <v>14</v>
-      </c>
-      <c r="C14" s="20"/>
-      <c r="D14" s="30" t="s">
-        <v>116</v>
-      </c>
-      <c r="E14" s="31"/>
-      <c r="F14" s="31"/>
-      <c r="G14" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="H14" s="30"/>
-      <c r="I14" s="31"/>
-      <c r="J14" s="32"/>
-      <c r="K14" s="33" t="s">
-        <v>50</v>
-      </c>
-      <c r="L14" s="34"/>
-      <c r="M14" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="N14" s="22"/>
-      <c r="O14" s="22"/>
-      <c r="P14" s="23"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A15" s="46"/>
-      <c r="B15" s="18" t="s">
-        <v>4</v>
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="30" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E15" s="31"/>
       <c r="F15" s="31"/>
       <c r="G15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="H15" s="30" t="s">
-        <v>117</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="H15" s="30"/>
       <c r="I15" s="31"/>
       <c r="J15" s="32"/>
       <c r="K15" s="33" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="L15" s="34"/>
       <c r="M15" s="21" t="s">
-        <v>61</v>
+        <v>119</v>
       </c>
       <c r="N15" s="22"/>
       <c r="O15" s="22"/>
       <c r="P15" s="23"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16">
       <c r="A16" s="46"/>
       <c r="B16" s="18" t="s">
-        <v>90</v>
+        <v>4</v>
       </c>
       <c r="C16" s="20"/>
-      <c r="D16" s="30"/>
+      <c r="D16" s="30" t="s">
+        <v>118</v>
+      </c>
       <c r="E16" s="31"/>
       <c r="F16" s="31"/>
-      <c r="G16" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="H16" s="31"/>
+      <c r="G16" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H16" s="30" t="s">
+        <v>117</v>
+      </c>
       <c r="I16" s="31"/>
       <c r="J16" s="32"/>
-      <c r="K16" s="15"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="21"/>
+      <c r="K16" s="33" t="s">
+        <v>60</v>
+      </c>
+      <c r="L16" s="34"/>
+      <c r="M16" s="21" t="s">
+        <v>61</v>
+      </c>
       <c r="N16" s="22"/>
       <c r="O16" s="22"/>
       <c r="P16" s="23"/>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16">
       <c r="A17" s="46"/>
       <c r="B17" s="18" t="s">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="C17" s="20"/>
       <c r="D17" s="30"/>
       <c r="E17" s="31"/>
       <c r="F17" s="31"/>
-      <c r="G17" s="31"/>
+      <c r="G17" s="17" t="s">
+        <v>91</v>
+      </c>
       <c r="H17" s="31"/>
       <c r="I17" s="31"/>
       <c r="J17" s="32"/>
-      <c r="K17" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="L17" s="34"/>
-      <c r="M17" s="21" t="s">
-        <v>94</v>
-      </c>
+      <c r="K17" s="15"/>
+      <c r="L17" s="16"/>
+      <c r="M17" s="21"/>
       <c r="N17" s="22"/>
       <c r="O17" s="22"/>
       <c r="P17" s="23"/>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16">
       <c r="A18" s="46"/>
-      <c r="B18" s="35" t="s">
+      <c r="B18" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="20"/>
+      <c r="D18" s="30"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="31"/>
+      <c r="G18" s="31"/>
+      <c r="H18" s="31"/>
+      <c r="I18" s="31"/>
+      <c r="J18" s="32"/>
+      <c r="K18" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="L18" s="34"/>
+      <c r="M18" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="N18" s="22"/>
+      <c r="O18" s="22"/>
+      <c r="P18" s="23"/>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="A19" s="46"/>
+      <c r="B19" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="36"/>
-      <c r="D18" s="36"/>
-      <c r="E18" s="36"/>
-      <c r="F18" s="36"/>
-      <c r="G18" s="36"/>
-      <c r="H18" s="36"/>
-      <c r="I18" s="36"/>
-      <c r="J18" s="37"/>
-      <c r="K18" s="35"/>
-      <c r="L18" s="37"/>
-      <c r="M18" s="35"/>
-      <c r="N18" s="36"/>
-      <c r="O18" s="36"/>
-      <c r="P18" s="37"/>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A19" s="46"/>
-      <c r="B19" s="12" t="s">
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="36"/>
+      <c r="H19" s="36"/>
+      <c r="I19" s="36"/>
+      <c r="J19" s="37"/>
+      <c r="K19" s="35"/>
+      <c r="L19" s="37"/>
+      <c r="M19" s="35"/>
+      <c r="N19" s="36"/>
+      <c r="O19" s="36"/>
+      <c r="P19" s="37"/>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="A20" s="46"/>
+      <c r="B20" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="33" t="s">
+      <c r="C20" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="D19" s="38"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="15" t="s">
+      <c r="D20" s="38"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="G19" s="33" t="s">
+      <c r="G20" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="H19" s="34"/>
-      <c r="I19" s="33" t="s">
+      <c r="H20" s="34"/>
+      <c r="I20" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="J19" s="34"/>
-      <c r="K19" s="39"/>
-      <c r="L19" s="40"/>
-      <c r="M19" s="39"/>
-      <c r="N19" s="41"/>
-      <c r="O19" s="41"/>
-      <c r="P19" s="40"/>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A20" s="46"/>
-      <c r="B20" s="8">
+      <c r="J20" s="34"/>
+      <c r="K20" s="39"/>
+      <c r="L20" s="40"/>
+      <c r="M20" s="39"/>
+      <c r="N20" s="41"/>
+      <c r="O20" s="41"/>
+      <c r="P20" s="40"/>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="A21" s="46"/>
+      <c r="B21" s="8">
         <v>1</v>
       </c>
-      <c r="C20" s="24" t="s">
+      <c r="C21" s="24" t="s">
         <v>123</v>
       </c>
-      <c r="D20" s="25"/>
-      <c r="E20" s="26"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="24" t="s">
-        <v>122</v>
-      </c>
-      <c r="H20" s="26"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="4"/>
-      <c r="K20" s="27"/>
-      <c r="L20" s="28"/>
-      <c r="M20" s="27"/>
-      <c r="N20" s="29"/>
-      <c r="O20" s="29"/>
-      <c r="P20" s="28"/>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A21" s="46"/>
-      <c r="B21" s="24"/>
-      <c r="C21" s="25"/>
       <c r="D21" s="25"/>
       <c r="E21" s="26"/>
       <c r="F21" s="3"/>
-      <c r="G21" s="24"/>
+      <c r="G21" s="24" t="s">
+        <v>122</v>
+      </c>
       <c r="H21" s="26"/>
       <c r="I21" s="3"/>
       <c r="J21" s="4"/>
@@ -2548,10 +2582,28 @@
       <c r="O21" s="29"/>
       <c r="P21" s="28"/>
     </row>
+    <row r="22" spans="1:16">
+      <c r="A22" s="46"/>
+      <c r="B22" s="24"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="26"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="4"/>
+      <c r="K22" s="27"/>
+      <c r="L22" s="28"/>
+      <c r="M22" s="27"/>
+      <c r="N22" s="29"/>
+      <c r="O22" s="29"/>
+      <c r="P22" s="28"/>
+    </row>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="A13:P13"/>
-    <mergeCell ref="A14:A21"/>
+    <mergeCell ref="A14:P14"/>
+    <mergeCell ref="A15:A22"/>
     <mergeCell ref="A7:P7"/>
     <mergeCell ref="D4:G4"/>
     <mergeCell ref="I1:M1"/>
@@ -2565,43 +2617,43 @@
     <mergeCell ref="D3:G3"/>
     <mergeCell ref="I4:M4"/>
     <mergeCell ref="D5:M5"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="H14:J14"/>
-    <mergeCell ref="K14:L14"/>
-    <mergeCell ref="M14:P14"/>
     <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:F15"/>
     <mergeCell ref="H15:J15"/>
     <mergeCell ref="K15:L15"/>
     <mergeCell ref="M15:P15"/>
-    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="M16:P16"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="M22:P22"/>
+    <mergeCell ref="B19:J19"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="M19:P19"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="M20:P20"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="D2:G2"/>
+    <mergeCell ref="I2:M2"/>
+    <mergeCell ref="C21:E21"/>
     <mergeCell ref="G21:H21"/>
     <mergeCell ref="K21:L21"/>
     <mergeCell ref="M21:P21"/>
-    <mergeCell ref="B18:J18"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="M17:P17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:J18"/>
     <mergeCell ref="K18:L18"/>
     <mergeCell ref="M18:P18"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="M19:P19"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="D2:G2"/>
-    <mergeCell ref="I2:M2"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="M20:P20"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="M16:P16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:J17"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="M17:P17"/>
-    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D15:F15"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2611,24 +2663,24 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45413367-06F1-4BFA-A7B3-B5E24549FF02}">
   <dimension ref="A1:P9"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="4.33203125" customWidth="1"/>
-    <col min="2" max="2" width="4.5" customWidth="1"/>
-    <col min="3" max="3" width="8.1640625" customWidth="1"/>
+    <col min="2" max="2" width="4.44140625" customWidth="1"/>
+    <col min="3" max="3" width="8.109375" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="4.9140625" customWidth="1"/>
-    <col min="6" max="6" width="15.08203125" customWidth="1"/>
+    <col min="5" max="5" width="4.88671875" customWidth="1"/>
+    <col min="6" max="6" width="15.109375" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
-    <col min="9" max="9" width="4.75" customWidth="1"/>
+    <col min="9" max="9" width="4.77734375" customWidth="1"/>
     <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="6.08203125" customWidth="1"/>
-    <col min="12" max="12" width="7.4140625" customWidth="1"/>
+    <col min="11" max="11" width="6.109375" customWidth="1"/>
+    <col min="12" max="12" width="7.44140625" customWidth="1"/>
     <col min="13" max="13" width="9" customWidth="1"/>
-    <col min="14" max="14" width="6.5" customWidth="1"/>
+    <col min="14" max="14" width="6.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16">
       <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
@@ -2654,7 +2706,7 @@
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16">
       <c r="A2" s="50" t="s">
         <v>4</v>
       </c>
@@ -2680,7 +2732,7 @@
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16">
       <c r="A3" s="50" t="s">
         <v>9</v>
       </c>
@@ -2702,7 +2754,7 @@
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16">
       <c r="A4" s="50" t="s">
         <v>10</v>
       </c>
@@ -2722,7 +2774,7 @@
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16">
       <c r="A5" s="30"/>
       <c r="B5" s="31"/>
       <c r="C5" s="31"/>
@@ -2740,7 +2792,7 @@
       <c r="O5" s="31"/>
       <c r="P5" s="32"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16">
       <c r="A6" s="47" t="s">
         <v>1</v>
       </c>
@@ -2760,7 +2812,7 @@
       <c r="O6" s="47"/>
       <c r="P6" s="47"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16">
       <c r="A7" s="2" t="s">
         <v>20</v>
       </c>
@@ -2810,7 +2862,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16">
       <c r="A8" s="7">
         <v>1</v>
       </c>
@@ -2850,7 +2902,7 @@
       <c r="O8" s="7"/>
       <c r="P8" s="1"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
@@ -2887,4 +2939,10 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{0a217bfd-7fc6-4e23-babe-07368f99370d}" enabled="1" method="Standard" siteId="{fda9decf-e892-43ac-9d9f-1a493f9f98d0}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>